--- a/docs/templates/STES-v1.1-raw-extraction-template.xlsx
+++ b/docs/templates/STES-v1.1-raw-extraction-template.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118.83203125" customWidth="1" min="1" max="1"/>
@@ -462,7 +462,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -491,7 +490,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -527,7 +525,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -643,20 +640,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16. Partially filled orders are NOT ignored: 'Partially filled', 'Partially filled, canceled' and 'Partial fill' statuses are extracted exactly like a normal BUY/SELL row (Ticker, Trade Date, BUY/SELL, Quantity, Price as printed). Never estimate or calculate the executed quantity, never discard the row — write 'Needs Confirmation' in Extraction Notes so it is confirmed later against the broker invoice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>The 'Examples' sheet shows correctly filled rows, including the same execution observed by two documents.</t>
-        </is>
-      </c>
-    </row>
+          <t>16. Order Status column: write the broker's own status text verbatim (e.g. 'Fulfilled', 'Partially filled', 'Partially filled, canceled', 'Partial fill', 'Cancelled'). A 'Partially filled'/'Partial fill' execution is NEVER ignored: extract it exactly like a normal BUY/SELL row (Ticker, Trade Date, BUY/SELL, Quantity, Price as printed) — never estimate or calculate the executed quantity, never discard the row. (Legacy compatibility: writing exactly 'Needs Confirmation' into Extraction Notes, with Order Status left blank, still works too.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>17. Order Status = 'Cancelled' (zero shares ever executed): still record the row — Ticker, Trade Date, and BUY/SELL are still required — but leave Quantity and Price blank unless the document actually prints an executed amount (it should not, for a fully cancelled order). This becomes an audit-only record, never a transaction — it is never treated as a Buy or Sell, never confirmed, never affects the ledger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
+        <is>
+          <t>The 'Examples' sheet shows correctly filled rows, including the same execution observed by two documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Do not submit the example rows. Fill 'Documents' and 'Observations' only.</t>
         </is>
@@ -862,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.83203125" customWidth="1" min="1" max="1"/>
@@ -1018,6 +1022,11 @@
           <t>Extraction Notes</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1030,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.83203125" customWidth="1" min="1" max="1"/>
@@ -1374,6 +1383,11 @@
           <t>Extraction Notes</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1682,6 +1696,150 @@
       <c r="Y14" t="inlineStr">
         <is>
           <t>Read from Earned Cash Dividends list; per-share rate shown on screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OBS-0005</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DOC-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ABUK</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Abu Qir Fertilizers and Chemicals</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>EGX</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>29</v>
+      </c>
+      <c r="K15" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1189.93</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>LIMIT</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Order state screen shows Partially filled, canceled — 29 of 190 shares executed</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Partially filled, canceled</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OBS-0006</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>DOC-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HRHO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Palm Hills Development</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>EGX</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>LIMIT</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Order state screen shows Cancelled — zero shares executed, kept for audit only</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
